--- a/03_Charts/VAE/FinancialRatios/XGBoost/StrategyC/Error_Summary.xlsx
+++ b/03_Charts/VAE/FinancialRatios/XGBoost/StrategyC/Error_Summary.xlsx
@@ -20,19 +20,19 @@
     <t xml:space="preserve">Count</t>
   </si>
   <si>
+    <t xml:space="preserve">Median_Return on Assets (ROA)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Median_Self-Financing Ratio</t>
   </si>
   <si>
-    <t xml:space="preserve">Median_Return on Assets (ROA)</t>
+    <t xml:space="preserve">Median_Net Debt Ratio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Median_Return on Fixed Assets</t>
   </si>
   <si>
     <t xml:space="preserve">Median_Cash to Current Assets</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Median_Return on Fixed Assets</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Median_Net Debt Ratio</t>
   </si>
   <si>
     <t xml:space="preserve">True Negative</t>
@@ -401,22 +401,22 @@
         <v>7</v>
       </c>
       <c r="B2" t="n">
-        <v>118843</v>
+        <v>125303</v>
       </c>
       <c r="C2" t="n">
-        <v>0.242493175614195</v>
+        <v>0.204210962993375</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0503672612801679</v>
+        <v>0.256990711671121</v>
       </c>
       <c r="E2" t="n">
-        <v>0.238493723849372</v>
+        <v>-0.267390135406123</v>
       </c>
       <c r="F2" t="n">
-        <v>0.115703257390322</v>
+        <v>0.159366866585644</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4375</v>
+        <v>0.216071046121157</v>
       </c>
     </row>
     <row r="3">
@@ -424,22 +424,22 @@
         <v>8</v>
       </c>
       <c r="B3" t="n">
-        <v>41187</v>
+        <v>34727</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.0854700854700855</v>
+        <v>-0.952897285783267</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.0270162892332141</v>
+        <v>-1.01252477976563</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0145454545454545</v>
+        <v>0.921716609669432</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.0474198047419805</v>
+        <v>-0.975266629102118</v>
       </c>
       <c r="G3" t="n">
-        <v>0.963031299272032</v>
+        <v>-0.66456972037349</v>
       </c>
     </row>
     <row r="4">
@@ -447,22 +447,22 @@
         <v>9</v>
       </c>
       <c r="B4" t="n">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="C4" t="n">
-        <v>0.146341463414634</v>
+        <v>-0.0523272749485278</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0310492505353319</v>
+        <v>-0.016486000945995</v>
       </c>
       <c r="E4" t="n">
-        <v>0.117763483424048</v>
+        <v>0.081935835322343</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0817610062893082</v>
+        <v>-0.0291620014485401</v>
       </c>
       <c r="G4" t="n">
-        <v>0.613496932515337</v>
+        <v>-0.0660168052744195</v>
       </c>
     </row>
     <row r="5">
@@ -470,22 +470,22 @@
         <v>10</v>
       </c>
       <c r="B5" t="n">
-        <v>1137</v>
+        <v>1142</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.197080291970803</v>
+        <v>-1.20161944377107</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.0656455142231947</v>
+        <v>-1.17805016483111</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0151953690303907</v>
+        <v>1.07982771479938</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.196444444444444</v>
+        <v>-1.20370996458539</v>
       </c>
       <c r="G5" t="n">
-        <v>1.01365546218487</v>
+        <v>-0.639511653263057</v>
       </c>
     </row>
   </sheetData>
